--- a/artfynd/A 11067-2023 artfynd.xlsx
+++ b/artfynd/A 11067-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11067-2023 artfynd.xlsx
+++ b/artfynd/A 11067-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100496776</v>
+        <v>100496731</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497896.190218026</v>
+        <v>497872</v>
       </c>
       <c r="R2" t="n">
-        <v>6722413.786493189</v>
+        <v>6722407</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-05-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100496738</v>
+        <v>100496765</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497918.30437945</v>
+        <v>497876</v>
       </c>
       <c r="R3" t="n">
-        <v>6722416.717181729</v>
+        <v>6722479</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2022-05-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100496746</v>
+        <v>100496767</v>
       </c>
       <c r="B4" t="n">
-        <v>5426</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101410</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497871.6086257485</v>
+        <v>497906</v>
       </c>
       <c r="R4" t="n">
-        <v>6722393.19598566</v>
+        <v>6722388</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2022-05-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-05-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100496765</v>
+        <v>100496776</v>
       </c>
       <c r="B5" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497876.5735184965</v>
+        <v>497896</v>
       </c>
       <c r="R5" t="n">
-        <v>6722479.536909856</v>
+        <v>6722414</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1034,9 @@
           <t>2022-05-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-05-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,53 +1063,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100496731</v>
+        <v>112342543</v>
       </c>
       <c r="B6" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lappholarna, Dlr</t>
+          <t>Lerbergsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497872.1084350256</v>
+        <v>497914</v>
       </c>
       <c r="R6" t="n">
-        <v>6722407.422945262</v>
+        <v>6722404</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,22 +1129,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,49 +1149,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100496767</v>
+        <v>100496738</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497905.5114449852</v>
+        <v>497918</v>
       </c>
       <c r="R7" t="n">
-        <v>6722387.779520162</v>
+        <v>6722417</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1308,19 +1229,9 @@
           <t>2022-05-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-05-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1258,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100496769</v>
+        <v>100496745</v>
       </c>
       <c r="B8" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497917.3244456195</v>
+        <v>497903</v>
       </c>
       <c r="R8" t="n">
-        <v>6722421.623673523</v>
+        <v>6722433</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1420,19 +1326,9 @@
           <t>2022-05-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-05-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1355,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112342543</v>
+        <v>100496769</v>
       </c>
       <c r="B9" t="n">
-        <v>94095</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,38 +1366,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lerbergsmyran, Dlr</t>
+          <t>Lappholarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497914</v>
+        <v>497917</v>
       </c>
       <c r="R9" t="n">
-        <v>6722405</v>
+        <v>6722422</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1530,12 +1420,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,15 +1440,112 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>John-Olof Halvarsson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>John-Olof Halvarsson</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100496746</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lappholarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>497871</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6722393</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-05-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-05-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11067-2023 artfynd.xlsx
+++ b/artfynd/A 11067-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100496731</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100496765</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100496767</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100496776</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112342543</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100496738</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100496745</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100496769</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,8 +1591,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100496746</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>